--- a/immunizations/v1.0.0/ValueSet-IMMZD18SPolioIPVOnlyVS.xlsx
+++ b/immunizations/v1.0.0/ValueSet-IMMZD18SPolioIPVOnlyVS.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T12:00:06+00:00</t>
+    <t>2026-10-02T09:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
